--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE6AB87-4F32-44B4-B0E6-A8AB76EFD6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91C4BF0-B49B-407B-9305-4CCA823B330B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 19-12-2025'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 29-01-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91C4BF0-B49B-407B-9305-4CCA823B330B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B47B46B-B8E4-439D-89CE-D4A75CC85073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 29-01-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 02-02-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B47B46B-B8E4-439D-89CE-D4A75CC85073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{606F764B-0E18-4CC7-9849-7DB760379031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 02-02-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 20-02-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{606F764B-0E18-4CC7-9849-7DB760379031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1455A6C3-9FEF-4DD4-9F66-7AB7332958E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 20-02-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 04-03-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1455A6C3-9FEF-4DD4-9F66-7AB7332958E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9173EC2C-440B-4E37-BB1A-4C0AF7414BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 04-03-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 06-03-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9173EC2C-440B-4E37-BB1A-4C0AF7414BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4739D3D-D36E-49CA-987D-4A45A9C2E7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4739D3D-D36E-49CA-987D-4A45A9C2E7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86A57C7-76A2-4121-B816-08946650842F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86A57C7-76A2-4121-B816-08946650842F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315825FA-3CF7-49C1-8D53-3EB4565A4C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 06-03-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 09-03-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315825FA-3CF7-49C1-8D53-3EB4565A4C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56C1A37-6678-4179-B36E-041261CE0C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56C1A37-6678-4179-B36E-041261CE0C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FDAB9D-6326-4D29-9F8A-A9455934D65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 09-03-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 11-03-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FDAB9D-6326-4D29-9F8A-A9455934D65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DADFEC-72F7-414F-A0A0-E217203F5F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DADFEC-72F7-414F-A0A0-E217203F5F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F45311-AA6F-48B7-AA8D-95BA03DA7C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 11-03-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 20-03-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F45311-AA6F-48B7-AA8D-95BA03DA7C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F9139D-6F9A-43DC-8674-9B8769B7F62B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 20-03-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 25-03-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F9139D-6F9A-43DC-8674-9B8769B7F62B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36C671F-00AC-43AE-8B86-23E5B5D8576C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 25-03-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 08-04-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36C671F-00AC-43AE-8B86-23E5B5D8576C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645D14EE-D26F-444A-A292-FC596994848A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 08-04-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 10-04-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645D14EE-D26F-444A-A292-FC596994848A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAD4C85-1A63-442E-9F44-A4B5DBD774B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAD4C85-1A63-442E-9F44-A4B5DBD774B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1C310D-8F8B-40BC-B32C-84CC355ECAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 10-04-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 14-04-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1C310D-8F8B-40BC-B32C-84CC355ECAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDFF191-7FB8-4A52-AAAF-073D338D4456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 14-04-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 24-04-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDFF191-7FB8-4A52-AAAF-073D338D4456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3311A80-988F-4A97-9E12-E67862092AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3311A80-988F-4A97-9E12-E67862092AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CA13EA-3B6F-4A9A-823D-0BDA5EFD649C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 24-04-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 27-04-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CA13EA-3B6F-4A9A-823D-0BDA5EFD649C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8862D0CF-B437-4D8D-8B10-406DA4A24B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 27-04-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 06-05-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8862D0CF-B437-4D8D-8B10-406DA4A24B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F95230-84B5-47F4-A805-E0774A2FFC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 06-05-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 01-06-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F95230-84B5-47F4-A805-E0774A2FFC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FCC97A-E30E-430F-80C1-E25CEE6CDA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 01-06-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 02-06-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FCC97A-E30E-430F-80C1-E25CEE6CDA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C72A1BC-7EC3-4890-A575-B62B8DAB53ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C72A1BC-7EC3-4890-A575-B62B8DAB53ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B34135-973E-45E5-9343-335D53F73B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 02-06-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 05-06-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91C4BF0-B49B-407B-9305-4CCA823B330B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B811957-F329-4195-8647-41061A366D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C8CFE4-C74C-4EA4-88DA-1D5DFAB3B7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BB7861-2BA2-486D-8803-5092271FE40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BB7861-2BA2-486D-8803-5092271FE40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD4BB14-A532-45AE-A869-3FD2704B9654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD4BB14-A532-45AE-A869-3FD2704B9654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE58F2B5-B77C-4000-9797-645E03F81B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 09-06-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 15-06-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE58F2B5-B77C-4000-9797-645E03F81B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FFAF7E-9006-43C0-9A37-99B7DB40EB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 15-06-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 22-06-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FFAF7E-9006-43C0-9A37-99B7DB40EB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0188E7A9-F942-4CE0-B7E2-428AAC5571F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 22-06-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 23-06-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0188E7A9-F942-4CE0-B7E2-428AAC5571F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A088A285-9B80-443A-8F25-832F853B3DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FFAF7E-9006-43C0-9A37-99B7DB40EB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB0C443-C86A-461C-9C42-334C8176677E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 22-06-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 23-06-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB0C443-C86A-461C-9C42-334C8176677E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA76A6F-5B1B-4D2F-AF1A-2EE2D082BA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 23-06-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 25-06-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA76A6F-5B1B-4D2F-AF1A-2EE2D082BA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FF55C0-B3A4-4CEA-885B-A4610A03CE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 25-06-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 30-06-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FF55C0-B3A4-4CEA-885B-A4610A03CE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E1E6DD-8AD0-4D05-98F3-A09DC2A4E428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E1E6DD-8AD0-4D05-98F3-A09DC2A4E428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228F8630-B069-4083-891F-920C557BA69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 30-06-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 01-07-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228F8630-B069-4083-891F-920C557BA69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F91427-C382-4A5E-9D92-BB6A17777E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 01-07-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 02-07-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228F8630-B069-4083-891F-920C557BA69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3048A22-46C3-4CCA-ACAE-5834743A758C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 01-07-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 03-07-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F91427-C382-4A5E-9D92-BB6A17777E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F84FB9-366E-4081-86F6-9F20CF7B23A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 02-07-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 03-07-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F84FB9-366E-4081-86F6-9F20CF7B23A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04899038-14DE-4FE3-AC8D-61B7A46EA225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 03-07-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 09-07-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04899038-14DE-4FE3-AC8D-61B7A46EA225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FF9A8D-B373-4610-9831-28E5AF4CCC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 09-07-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 19-08-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FF9A8D-B373-4610-9831-28E5AF4CCC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FA879F-74FB-49E9-BA1B-E879FD7708A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 19-08-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 21-08-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FA879F-74FB-49E9-BA1B-E879FD7708A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B25C80A-FD17-4E44-8E2F-777DD20F8052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 21-08-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 27-08-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B25C80A-FD17-4E44-8E2F-777DD20F8052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EB762C-B630-4231-96AE-199ECE1D6654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 27-08-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 02-09-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EB762C-B630-4231-96AE-199ECE1D6654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CF3E75-31C4-4394-B3EA-182B0AAE8BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 02-09-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 06-09-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CF3E75-31C4-4394-B3EA-182B0AAE8BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58DFF997-BA54-4FE8-B5EE-2A8FE72F511C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58DFF997-BA54-4FE8-B5EE-2A8FE72F511C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE2F5DE-F1C5-4ED1-9560-A6CB95453CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 06-09-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 07-09-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE2F5DE-F1C5-4ED1-9560-A6CB95453CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCBD379-C54F-4C6D-BB06-EEA25950BF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 07-09-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 09-09-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCBD379-C54F-4C6D-BB06-EEA25950BF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DACC84-3D86-4B76-99D1-57FDAEB7C902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
